--- a/backend/storage/imports/Master_SBM/5. SATUAN BIAYA PENERJEMAHAN DAN PENGETIKAN.xlsx
+++ b/backend/storage/imports/Master_SBM/5. SATUAN BIAYA PENERJEMAHAN DAN PENGETIKAN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B48D30B-A894-4087-8CA1-4177EA2E02B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732E69FA-5E38-478D-9C5A-A493A5F29EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D4697CA-9BAE-4E0A-844F-E7642B3021EA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>NO</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>SATUAN BIAYA PENERJEMAHAN DAN PENGETIKAN</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -115,7 +112,7 @@
     <numFmt numFmtId="166" formatCode="[$Rp-421]#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +133,6 @@
     </font>
     <font>
       <sz val="8.5"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="1"/>
@@ -157,7 +147,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -180,11 +170,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,22 +213,34 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D28DEA-BA90-49F9-ABF4-DE230EF46D19}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -533,73 +566,61 @@
     <col min="4" max="4" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6">
+        <v>5</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>-1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B4" s="2">
         <v>-2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C4" s="2">
         <v>-3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>250000</v>
       </c>
     </row>
@@ -607,13 +628,13 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>420000</v>
       </c>
     </row>
@@ -621,13 +642,13 @@
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>410000</v>
       </c>
     </row>
@@ -635,13 +656,13 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>450000</v>
       </c>
     </row>
@@ -649,13 +670,13 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>366000</v>
       </c>
     </row>
@@ -663,13 +684,13 @@
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>414000</v>
       </c>
     </row>
@@ -677,31 +698,70 @@
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>300000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+    <row r="12" spans="1:4" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
         <v>5.2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="B14" s="2">
+        <v>-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D15" s="4">
         <v>174000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>